--- a/files/港岛-西营盘及上环-15 Western Street.xlsx
+++ b/files/港岛-西营盘及上环-15 Western Street.xlsx
@@ -763,7 +763,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2021-06-28</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -825,7 +825,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2021-07-12</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -887,7 +887,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2022-04-18</t>
+          <t>2022-04-19</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2022-02-22</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2021-11-30</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2021-04-07</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2021-03-09</t>
+          <t>2021-03-10</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2022-04-20</t>
+          <t>2022-04-21</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2021-12-10</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2023-12-11</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2021-12-09</t>
+          <t>2021-12-10</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2021-11-30</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2021-08-25</t>
+          <t>2021-08-26</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
+          <t>2021-05-02</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2022-09-27</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2020-10-21</t>
+          <t>2020-10-22</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2020-06-18</t>
+          <t>2020-06-19</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2021-03-09</t>
+          <t>2021-03-10</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2021-12-22</t>
+          <t>2021-12-23</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2020-07-19</t>
+          <t>2020-07-20</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2020-02-03</t>
+          <t>2020-02-04</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2020-06-22</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2021-06-06</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2020-07-08</t>
+          <t>2020-07-09</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2020-02-04</t>
+          <t>2020-02-05</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2020-02-03</t>
+          <t>2020-02-04</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2021-08-08</t>
+          <t>2021-08-09</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2020-04-15</t>
+          <t>2020-04-16</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2020-02-05</t>
+          <t>2020-02-06</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
+          <t>2021-09-13</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2020-02-03</t>
+          <t>2020-02-04</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2020-02-03</t>
+          <t>2020-02-04</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
+          <t>2020-12-31</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2022-07-31</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2020-05-07</t>
+          <t>2020-05-08</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2020-02-04</t>
+          <t>2020-02-05</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2021-06-28</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2021-09-29</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2021-12-08</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2020-02-05</t>
+          <t>2020-02-06</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2020-02-06</t>
+          <t>2020-02-07</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2020-02-04</t>
+          <t>2020-02-05</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2021-04-06</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2021-07-05</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2020-02-06</t>
+          <t>2020-02-07</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2020-01-09</t>
+          <t>2020-01-10</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2022-04-20</t>
+          <t>2022-04-21</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2021-03-08</t>
+          <t>2021-03-09</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2022-05-04</t>
+          <t>2022-05-05</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6157,7 +6157,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2020-02-09</t>
+          <t>2020-02-10</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2021-05-25</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2020-04-20</t>
+          <t>2020-04-21</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2020-02-04</t>
+          <t>2020-02-05</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2021-08-26</t>
+          <t>2021-08-27</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2020-05-07</t>
+          <t>2020-05-08</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2021-06-14</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2021-09-02</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
+          <t>2020-07-15</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7025,7 +7025,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2020-10-13</t>
+          <t>2020-10-14</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2020-05-25</t>
+          <t>2020-05-26</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
+          <t>2021-11-10</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7382,7 +7382,7 @@
           <t>A | 620呎 (3房)
 $2588万
 $41,748/呎
-(21年-07月-12日)</t>
+(21年-07月-13日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -7390,7 +7390,7 @@
           <t>B | 564呎 (2房)
 $2272万
 $40,284/呎
-(21年-06月-28日)</t>
+(21年-06月-29日)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr"/>
@@ -7408,7 +7408,7 @@
           <t>A | 620呎 (3房)
 $2139万
 $34,502/呎
-(22年-02月-22日)</t>
+(22年-02月-23日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -7416,7 +7416,7 @@
           <t>B | 530呎 (2房)
 $1807万
 $34,102/呎
-(22年-04月-18日)</t>
+(22年-04月-19日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr"/>
@@ -7434,7 +7434,7 @@
           <t>A | 620呎 (3房)
 $2045万
 $32,987/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -7442,7 +7442,7 @@
           <t>B | 530呎 (2房)
 $1722万
 $32,485/呎
-(21年-12月-12日)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr"/>
@@ -7460,7 +7460,7 @@
           <t>A | 620呎 (3房)
 $1971万
 $31,787/呎
-(21年-04月-07日)</t>
+(21年-04月-08日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -7468,7 +7468,7 @@
           <t>B | 530呎 (2房)
 $1714万
 $32,345/呎
-(21年-11月-30日)</t>
+(21年-12月-01日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr"/>
@@ -7486,7 +7486,7 @@
           <t>A | 661呎 (3房)
 $2414万
 $36,513/呎
-(21年-03月-09日)</t>
+(21年-03月-10日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -7494,7 +7494,7 @@
           <t>B | 530呎 (2房)
 $1610万
 $30,375/呎
-(21年-04月-07日)</t>
+(21年-04月-08日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr"/>
@@ -7512,7 +7512,7 @@
           <t>A | 308呎 (1房)
 $1120万
 $36,364/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -7520,7 +7520,7 @@
           <t>B | 341呎 (1房)
 $1115万
 $32,695/呎
-(22年-04月-20日)</t>
+(22年-04月-21日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -7528,7 +7528,7 @@
           <t>C | 212呎 (开放式)
 $756万
 $35,651/呎
-(24年-03月-26日)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -7536,7 +7536,7 @@
           <t>D | 212呎 (开放式)
 $756万
 $35,651/呎
-(24年-03月-26日)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -7544,7 +7544,7 @@
           <t>E | 344呎 (1房)
 $1141万
 $33,160/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
           <t>B | 341呎 (1房)
 $1097万
 $32,179/呎
-(21年-06月-24日)</t>
+(21年-06月-25日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -7575,7 +7575,7 @@
           <t>C | 212呎 (开放式)
 $720万
 $33,953/呎
-(24年-03月-26日)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -7583,7 +7583,7 @@
           <t>D | 212呎 (开放式)
 $720万
 $33,953/呎
-(24年-03月-26日)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -7591,7 +7591,7 @@
           <t>E | 344呎 (1房)
 $1097万
 $31,898/呎
-(21年-12月-09日)</t>
+(21年-12月-10日)</t>
         </is>
       </c>
     </row>
@@ -7606,7 +7606,7 @@
           <t>A | 307呎 (1房)
 $1024万
 $33,355/呎
-(21年-12月-09日)</t>
+(21年-12月-10日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -7614,7 +7614,7 @@
           <t>B | 341呎 (1房)
 $1065万
 $31,240/呎
-(21年-09月-23日)</t>
+(21年-09月-24日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -7622,7 +7622,7 @@
           <t>C | 212呎 (开放式)
 $703万
 $33,156/呎
-(23年-12月-11日)</t>
+(23年-12月-12日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -7630,7 +7630,7 @@
           <t>D | 212呎 (开放式)
 $698万
 $32,934/呎
-(24年-04月-10日)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -7638,7 +7638,7 @@
           <t>E | 344呎 (1房)
 $1065万
 $30,968/呎
-(21年-06月-02日)</t>
+(21年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
           <t>A | 307呎 (1房)
 $1016万
 $33,091/呎
-(21年-09月-09日)</t>
+(21年-09月-10日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -7661,7 +7661,7 @@
           <t>B | 340呎 (1房)
 $1050万
 $30,871/呎
-(21年-08月-25日)</t>
+(21年-08月-26日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -7669,7 +7669,7 @@
           <t>C | 212呎 (开放式)
 $699万
 $32,958/呎
-(24年-03月-17日)</t>
+(24年-03月-18日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -7677,7 +7677,7 @@
           <t>D | 212呎 (开放式)
 $699万
 $32,958/呎
-(24年-03月-17日)</t>
+(24年-03月-18日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -7685,7 +7685,7 @@
           <t>E | 344呎 (1房)
 $1050万
 $30,512/呎
-(21年-11月-30日)</t>
+(21年-12月-01日)</t>
         </is>
       </c>
     </row>
@@ -7700,7 +7700,7 @@
           <t>A | 308呎 (1房)
 $1008万
 $32,721/呎
-(22年-09月-26日)</t>
+(22年-09月-27日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -7708,7 +7708,7 @@
           <t>B | 341呎 (1房)
 $1044万
 $30,625/呎
-(21年-05月-24日)</t>
+(21年-05月-25日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -7716,7 +7716,7 @@
           <t>C | 212呎 (开放式)
 $691万
 $32,575/呎
-(24年-03月-17日)</t>
+(24年-03月-18日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -7724,7 +7724,7 @@
           <t>D | 212呎 (开放式)
 $691万
 $32,575/呎
-(24年-03月-17日)</t>
+(24年-03月-18日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -7732,7 +7732,7 @@
           <t>E | 344呎 (1房)
 $1050万
 $30,538/呎
-(21年-05月-01日)</t>
+(21年-05月-02日)</t>
         </is>
       </c>
     </row>
@@ -7747,7 +7747,7 @@
           <t>A | 307呎 (1房)
 $1000万
 $32,567/呎
-(21年-10月-14日)</t>
+(21年-10月-15日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -7755,7 +7755,7 @@
           <t>B | 341呎 (1房)
 $1017万
 $29,830/呎
-(21年-05月-23日)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -7763,7 +7763,7 @@
           <t>C | 212呎 (开放式)
 $610万
 $28,750/呎
-(26年-01月-07日)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -7771,7 +7771,7 @@
           <t>D | 212呎 (开放式)
 $687万
 $32,420/呎
-(24年-03月-17日)</t>
+(24年-03月-18日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -7779,7 +7779,7 @@
           <t>E | 344呎 (1房)
 $987万
 $28,703/呎
-(21年-05月-24日)</t>
+(21年-05月-25日)</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
           <t>A | 308呎 (1房)
 $929万
 $30,173/呎
-(25年-05月-28日)</t>
+(25年-05月-29日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -7802,7 +7802,7 @@
           <t>B | 340呎 (1房)
 $992万
 $29,171/呎
-(20年-10月-21日)</t>
+(20年-10月-22日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -7810,7 +7810,7 @@
           <t>C | 212呎 (开放式)
 $684万
 $32,269/呎
-(22年-08月-01日)</t>
+(22年-08月-02日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -7818,7 +7818,7 @@
           <t>D | 212呎 (开放式)
 $684万
 $32,269/呎
-(24年-03月-17日)</t>
+(24年-03月-18日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -7826,7 +7826,7 @@
           <t>E | 344呎 (1房)
 $964万
 $28,017/呎
-(21年-02月-25日)</t>
+(21年-02月-26日)</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
           <t>A | 308呎 (1房)
 $982万
 $31,886/呎
-(21年-12月-22日)</t>
+(21年-12月-23日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -7849,7 +7849,7 @@
           <t>B | 340呎 (1房)
 $1025万
 $30,156/呎
-(21年-03月-09日)</t>
+(21年-03月-10日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -7857,7 +7857,7 @@
           <t>C | 212呎 (开放式)
 $684万
 $32,259/呎
-(23年-10月-04日)</t>
+(23年-10月-05日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -7865,7 +7865,7 @@
           <t>D | 212呎 (开放式)
 $749万
 $35,330/呎
-(20年-06月-18日)</t>
+(20年-06月-19日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -7873,7 +7873,7 @@
           <t>E | 344呎 (1房)
 $962万
 $27,959/呎
-(21年-05月-23日)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7888,7 @@
           <t>A | 308呎 (1房)
 $920万
 $29,870/呎
-(25年-09月-21日)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -7896,7 +7896,7 @@
           <t>B | 340呎 (1房)
 $978万
 $28,774/呎
-(21年-06月-06日)</t>
+(21年-06月-07日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -7904,7 +7904,7 @@
           <t>C | 213呎 (开放式)
 $656万
 $30,808/呎
-(20年-06月-22日)</t>
+(20年-06月-23日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -7912,7 +7912,7 @@
           <t>D | 213呎 (开放式)
 $656万
 $30,808/呎
-(20年-02月-03日)</t>
+(20年-02月-04日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -7920,7 +7920,7 @@
           <t>E | 344呎 (1房)
 $996万
 $28,951/呎
-(20年-07月-19日)</t>
+(20年-07月-20日)</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7935,7 @@
           <t>A | 307呎 (1房)
 $947万
 $30,850/呎
-(21年-08月-08日)</t>
+(21年-08月-09日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -7943,7 +7943,7 @@
           <t>B | 341呎 (1房)
 $965万
 $28,296/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -7951,7 +7951,7 @@
           <t>C | 213呎 (开放式)
 $702万
 $32,934/呎
-(20年-02月-03日)</t>
+(20年-02月-04日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -7959,7 +7959,7 @@
           <t>D | 212呎 (开放式)
 $702万
 $33,090/呎
-(20年-02月-04日)</t>
+(20年-02月-05日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -7967,7 +7967,7 @@
           <t>E | 344呎 (1房)
 $971万
 $28,230/呎
-(20年-07月-08日)</t>
+(20年-07月-09日)</t>
         </is>
       </c>
     </row>
@@ -7982,7 +7982,7 @@
           <t>A | 307呎 (1房)
 $942万
 $30,697/呎
-(21年-09月-12日)</t>
+(21年-09月-13日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -7990,7 +7990,7 @@
           <t>B | 340呎 (1房)
 $958万
 $28,182/呎
-(21年-05月-26日)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -7998,7 +7998,7 @@
           <t>C | 212呎 (开放式)
 $636万
 $30,014/呎
-(20年-02月-05日)</t>
+(20年-02月-06日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -8006,7 +8006,7 @@
           <t>D | 213呎 (开放式)
 $667万
 $31,296/呎
-(20年-04月-15日)</t>
+(20年-04月-16日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -8014,7 +8014,7 @@
           <t>E | 344呎 (1房)
 $964万
 $28,035/呎
-(20年-06月-21日)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -8029,7 +8029,7 @@
           <t>A | 308呎 (1房)
 $938万
 $30,445/呎
-(22年-07月-31日)</t>
+(22年-08月-01日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -8037,7 +8037,7 @@
           <t>B | 341呎 (1房)
 $997万
 $29,238/呎
-(20年-12月-30日)</t>
+(20年-12月-31日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -8045,7 +8045,7 @@
           <t>C | 212呎 (开放式)
 $692万
 $32,651/呎
-(20年-02月-03日)</t>
+(20年-02月-04日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -8053,7 +8053,7 @@
           <t>D | 212呎 (开放式)
 $692万
 $32,651/呎
-(20年-02月-03日)</t>
+(20年-02月-04日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -8061,7 +8061,7 @@
           <t>E | 344呎 (1房)
 $925万
 $26,881/呎
-(21年-05月-26日)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -8076,7 +8076,7 @@
           <t>A | 308呎 (1房)
 $933万
 $30,292/呎
-(21年-12月-08日)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -8084,7 +8084,7 @@
           <t>B | 341呎 (1房)
 $1000万
 $29,323/呎
-(21年-09月-29日)</t>
+(21年-09月-30日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -8092,7 +8092,7 @@
           <t>C | 213呎 (开放式)
 $658万
 $30,878/呎
-(21年-06月-28日)</t>
+(21年-06月-29日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -8100,7 +8100,7 @@
           <t>D | 212呎 (开放式)
 $628万
 $29,613/呎
-(20年-02月-04日)</t>
+(20年-02月-05日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -8108,7 +8108,7 @@
           <t>E | 344呎 (1房)
 $951万
 $27,648/呎
-(20年-05月-07日)</t>
+(20年-05月-08日)</t>
         </is>
       </c>
     </row>
@@ -8123,7 +8123,7 @@
           <t>A | 308呎 (1房)
 $908万
 $29,464/呎
-(21年-07月-05日)</t>
+(21年-07月-06日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -8131,7 +8131,7 @@
           <t>B | 340呎 (1房)
 $939万
 $27,609/呎
-(21年-04月-06日)</t>
+(21年-04月-07日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -8139,7 +8139,7 @@
           <t>C | 213呎 (开放式)
 $683万
 $32,070/呎
-(20年-02月-04日)</t>
+(20年-02月-05日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -8147,7 +8147,7 @@
           <t>D | 212呎 (开放式)
 $624万
 $29,420/呎
-(20年-02月-06日)</t>
+(20年-02月-07日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -8155,7 +8155,7 @@
           <t>E | 344呎 (1房)
 $999万
 $29,038/呎
-(20年-02月-05日)</t>
+(20年-02月-06日)</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
           <t>A | 307呎 (1房)
 $885万
 $28,827/呎
-(21年-06月-02日)</t>
+(21年-06月-03日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -8178,7 +8178,7 @@
           <t>B | 341呎 (1房)
 $1000万
 $29,323/呎
-(22年-04月-20日)</t>
+(22年-04月-21日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -8186,7 +8186,7 @@
           <t>C | 213呎 (开放式)
 $652万
 $30,610/呎
-(20年-01月-09日)</t>
+(20年-01月-10日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -8194,7 +8194,7 @@
           <t>D | 212呎 (开放式)
 $654万
 $30,844/呎
-(23年-08月-02日)</t>
+(23年-08月-03日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -8202,7 +8202,7 @@
           <t>E | 344呎 (1房)
 $910万
 $26,459/呎
-(20年-02月-06日)</t>
+(20年-02月-07日)</t>
         </is>
       </c>
     </row>
@@ -8217,7 +8217,7 @@
           <t>A | 307呎 (1房)
 $870万
 $28,332/呎
-(21年-07月-08日)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -8225,7 +8225,7 @@
           <t>B | 341呎 (1房)
 $926万
 $27,150/呎
-(21年-05月-25日)</t>
+(21年-05月-26日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -8233,7 +8233,7 @@
           <t>C | 212呎 (开放式)
 $615万
 $29,024/呎
-(20年-02月-09日)</t>
+(20年-02月-10日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -8241,7 +8241,7 @@
           <t>D | 212呎 (开放式)
 $668万
 $31,509/呎
-(22年-05月-04日)</t>
+(22年-05月-05日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -8249,7 +8249,7 @@
           <t>E | 344呎 (1房)
 $900万
 $26,148/呎
-(21年-03月-08日)</t>
+(21年-03月-09日)</t>
         </is>
       </c>
     </row>
@@ -8264,7 +8264,7 @@
           <t>A | 308呎 (1房)
 $864万
 $28,045/呎
-(21年-08月-26日)</t>
+(21年-08月-27日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -8272,7 +8272,7 @@
           <t>B | 340呎 (1房)
 $980万
 $28,824/呎
-(21年-09月-27日)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -8280,7 +8280,7 @@
           <t>C | 213呎 (开放式)
 $640万
 $30,061/呎
-(21年-08月-17日)</t>
+(21年-08月-18日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -8288,7 +8288,7 @@
           <t>D | 212呎 (开放式)
 $633万
 $29,863/呎
-(20年-02月-04日)</t>
+(20年-02月-05日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -8296,7 +8296,7 @@
           <t>E | 344呎 (1房)
 $978万
 $28,445/呎
-(20年-04月-20日)</t>
+(20年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -8311,7 +8311,7 @@
           <t>A | 307呎 (1房)
 $858万
 $27,945/呎
-(20年-06月-21日)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -8319,7 +8319,7 @@
           <t>B | 341呎 (1房)
 $913万
 $26,777/呎
-(21年-03月-23日)</t>
+(21年-03月-24日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -8327,7 +8327,7 @@
           <t>C | 212呎 (开放式)
 $636万
 $30,005/呎
-(21年-09月-01日)</t>
+(21年-09月-02日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -8335,7 +8335,7 @@
           <t>D | 212呎 (开放式)
 $636万
 $30,005/呎
-(21年-06月-14日)</t>
+(21年-06月-15日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -8343,7 +8343,7 @@
           <t>E | 344呎 (1房)
 $930万
 $27,020/呎
-(20年-05月-07日)</t>
+(20年-05月-08日)</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
           <t>A | 307呎 (1房)
 $852万
 $27,752/呎
-(21年-11月-09日)</t>
+(21年-11月-10日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -8366,7 +8366,7 @@
           <t>B | 341呎 (1房)
 $907万
 $26,592/呎
-(21年-05月-26日)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -8374,7 +8374,7 @@
           <t>C | 213呎 (开放式)
 $594万
 $27,883/呎
-(20年-05月-25日)</t>
+(20年-05月-26日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -8382,7 +8382,7 @@
           <t>D | 213呎 (开放式)
 $622万
 $29,211/呎
-(20年-10月-13日)</t>
+(20年-10月-14日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -8390,7 +8390,7 @@
           <t>E | 344呎 (1房)
 $873万
 $25,387/呎
-(20年-07月-14日)</t>
+(20年-07月-15日)</t>
         </is>
       </c>
     </row>
